--- a/public/library/site-layout.xlsx
+++ b/public/library/site-layout.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="거점·창고 코드" sheetId="1" r:id="rId1"/>
+    <sheet name="창고코드 조견표" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -121,10 +122,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +157,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -399,12 +400,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F29"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="16.83203125"/>
+    <col min="2" max="2" customWidth="1" width="18.83203125"/>
+    <col min="3" max="3" customWidth="1" width="6.83203125"/>
+    <col min="4" max="4" customWidth="1" width="11.83203125"/>
+    <col min="5" max="5" customWidth="1" width="24.83203125"/>
+    <col min="6" max="6" customWidth="1" width="22.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,4 +803,103 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>창고코드 조견표</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>예시) 김포1A-01  =  거점코드(거점명) + 창고코드(한자리 숫자) + 건물(장소)코드(알파벳 대문자) + 라인(구역)코드(두자리 숫자)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>위치</v>
+      </c>
+      <c r="B4" t="str">
+        <v>거점코드(거점명)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>창고코드(한자리 숫자)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>건물(장소)코드(알파벳 대문자)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>라인(구역)코드(두자리 숫자)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>전체 코드</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>김포1공장 A동 라인1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>김포</v>
+      </c>
+      <c r="C5" t="str">
+        <v>1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A</v>
+      </c>
+      <c r="E5" t="str">
+        <v>-01</v>
+      </c>
+      <c r="F5" t="str">
+        <v>김포1A-01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>본사(도창) 2층 구역3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>본사</v>
+      </c>
+      <c r="C6" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" t="str">
+        <v>-02</v>
+      </c>
+      <c r="F6" t="str">
+        <v>본사1B-02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>라인(구역)코드는 창고 코드 뒤에 "-"와 두 자리 숫자로 붙입니다.</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A8:F8"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/library/site-layout.xlsx
+++ b/public/library/site-layout.xlsx
@@ -122,10 +122,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -157,10 +157,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -869,7 +869,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>본사(도창) 2층 구역3</v>
+        <v>본사(도창) 2층 구역2</v>
       </c>
       <c r="B6" t="str">
         <v>본사</v>
